--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/113.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/113.xlsx
@@ -426,13 +426,13 @@
         <v>-8.873740291070275</v>
       </c>
       <c r="E2">
-        <v>-19.13157754265878</v>
+        <v>-19.76254341156952</v>
       </c>
       <c r="F2">
-        <v>1.586362362381477</v>
+        <v>-0.6419194433923034</v>
       </c>
       <c r="G2">
-        <v>-16.97361200606504</v>
+        <v>-19.52886329548261</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.547856038920791</v>
       </c>
       <c r="E3">
-        <v>-20.27589575355304</v>
+        <v>-22.26095233481534</v>
       </c>
       <c r="F3">
-        <v>1.676099403126748</v>
+        <v>-0.2061841072739159</v>
       </c>
       <c r="G3">
-        <v>-16.68762401616539</v>
+        <v>-18.21190728855154</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.17021802020297</v>
       </c>
       <c r="E4">
-        <v>-20.48666451929204</v>
+        <v>-23.0137884962205</v>
       </c>
       <c r="F4">
-        <v>1.843287139298966</v>
+        <v>-0.7402317434913543</v>
       </c>
       <c r="G4">
-        <v>-16.44973381249487</v>
+        <v>-19.43664456355441</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.768815175866124</v>
       </c>
       <c r="E5">
-        <v>-20.62050356858873</v>
+        <v>-24.36503079842124</v>
       </c>
       <c r="F5">
-        <v>1.406936326200299</v>
+        <v>-0.3988118347535101</v>
       </c>
       <c r="G5">
-        <v>-15.81981145995579</v>
+        <v>-19.12943691382984</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.350723261971556</v>
       </c>
       <c r="E6">
-        <v>-21.05236149233022</v>
+        <v>-24.42703013606025</v>
       </c>
       <c r="F6">
-        <v>1.944253528556587</v>
+        <v>-0.1930677378179885</v>
       </c>
       <c r="G6">
-        <v>-15.31416209275913</v>
+        <v>-16.81776382565609</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.9312582672501</v>
       </c>
       <c r="E7">
-        <v>-21.47739047726814</v>
+        <v>-25.46038261987055</v>
       </c>
       <c r="F7">
-        <v>2.143590203631454</v>
+        <v>0.0001083688822589831</v>
       </c>
       <c r="G7">
-        <v>-15.41669698527021</v>
+        <v>-17.38219791770099</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.513576793731158</v>
       </c>
       <c r="E8">
-        <v>-22.8758738203169</v>
+        <v>-26.04685623165593</v>
       </c>
       <c r="F8">
-        <v>1.912795448067873</v>
+        <v>-0.09270688513181442</v>
       </c>
       <c r="G8">
-        <v>-14.59236225533404</v>
+        <v>-16.71622478388829</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.111865742388685</v>
       </c>
       <c r="E9">
-        <v>-23.11296660546249</v>
+        <v>-25.14138785382224</v>
       </c>
       <c r="F9">
-        <v>2.038495231238281</v>
+        <v>-0.02443532889528757</v>
       </c>
       <c r="G9">
-        <v>-13.62138645268472</v>
+        <v>-15.87196975786473</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.729574859762281</v>
       </c>
       <c r="E10">
-        <v>-24.27933848477409</v>
+        <v>-28.0769439584505</v>
       </c>
       <c r="F10">
-        <v>2.23002371517436</v>
+        <v>-0.1809727453697129</v>
       </c>
       <c r="G10">
-        <v>-13.35300877889461</v>
+        <v>-14.58225937415251</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.375891799426262</v>
       </c>
       <c r="E11">
-        <v>-24.4603551762827</v>
+        <v>-27.32092427981795</v>
       </c>
       <c r="F11">
-        <v>2.144322480415529</v>
+        <v>-0.06027050274039418</v>
       </c>
       <c r="G11">
-        <v>-13.43131841263232</v>
+        <v>-16.21358265625086</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.061220087120786</v>
       </c>
       <c r="E12">
-        <v>-25.90469837560714</v>
+        <v>-27.74534644923884</v>
       </c>
       <c r="F12">
-        <v>2.405882801319084</v>
+        <v>0.9275518265261967</v>
       </c>
       <c r="G12">
-        <v>-13.13816423484685</v>
+        <v>-15.57863839411505</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.787673503702655</v>
       </c>
       <c r="E13">
-        <v>-25.53076416289776</v>
+        <v>-28.70368023263807</v>
       </c>
       <c r="F13">
-        <v>2.831506256551498</v>
+        <v>0.9358951430071933</v>
       </c>
       <c r="G13">
-        <v>-12.87545979313303</v>
+        <v>-14.34016920688589</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.565751182205501</v>
       </c>
       <c r="E14">
-        <v>-26.78775080710286</v>
+        <v>-29.59516694697308</v>
       </c>
       <c r="F14">
-        <v>2.604058105295227</v>
+        <v>0.913494431700689</v>
       </c>
       <c r="G14">
-        <v>-12.6182251477588</v>
+        <v>-14.50577902143419</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.395489113830697</v>
       </c>
       <c r="E15">
-        <v>-27.87068102434913</v>
+        <v>-31.88154592446876</v>
       </c>
       <c r="F15">
-        <v>3.153525800715778</v>
+        <v>1.187138976276283</v>
       </c>
       <c r="G15">
-        <v>-11.85606628515254</v>
+        <v>-14.95728002984612</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-4.274353915178071</v>
       </c>
       <c r="E16">
-        <v>-29.35871041242557</v>
+        <v>-31.66744873033412</v>
       </c>
       <c r="F16">
-        <v>3.607616930112799</v>
+        <v>1.065060815390915</v>
       </c>
       <c r="G16">
-        <v>-11.69897124055101</v>
+        <v>-14.21402756586538</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.200107632007498</v>
       </c>
       <c r="E17">
-        <v>-29.33630352303561</v>
+        <v>-33.5011750314451</v>
       </c>
       <c r="F17">
-        <v>3.791584076396125</v>
+        <v>1.47590453942258</v>
       </c>
       <c r="G17">
-        <v>-11.79174449892275</v>
+        <v>-14.30970142409567</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.161160140434742</v>
       </c>
       <c r="E18">
-        <v>-30.16013257145902</v>
+        <v>-33.77848519425281</v>
       </c>
       <c r="F18">
-        <v>4.28943951241785</v>
+        <v>1.298112043759722</v>
       </c>
       <c r="G18">
-        <v>-11.79952755646175</v>
+        <v>-13.6932091113994</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.148600763025554</v>
       </c>
       <c r="E19">
-        <v>-29.95906379704445</v>
+        <v>-33.54944177165585</v>
       </c>
       <c r="F19">
-        <v>4.456496366540427</v>
+        <v>1.708983932283082</v>
       </c>
       <c r="G19">
-        <v>-11.67644565454542</v>
+        <v>-13.03024157653516</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.149507642137508</v>
       </c>
       <c r="E20">
-        <v>-32.31257513746684</v>
+        <v>-34.96979311568765</v>
       </c>
       <c r="F20">
-        <v>4.66826849306612</v>
+        <v>2.440778606529416</v>
       </c>
       <c r="G20">
-        <v>-11.82395296975026</v>
+        <v>-13.83961393616026</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.14731158909174</v>
       </c>
       <c r="E21">
-        <v>-32.60592289097271</v>
+        <v>-35.9734795662737</v>
       </c>
       <c r="F21">
-        <v>4.724075604992723</v>
+        <v>2.146227725441968</v>
       </c>
       <c r="G21">
-        <v>-11.22773204384824</v>
+        <v>-12.65681231329787</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.130490367447159</v>
       </c>
       <c r="E22">
-        <v>-32.22949348908512</v>
+        <v>-37.19442635008875</v>
       </c>
       <c r="F22">
-        <v>5.076792788369946</v>
+        <v>2.650287633310661</v>
       </c>
       <c r="G22">
-        <v>-11.15625719461885</v>
+        <v>-12.96237607102116</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.084960124354446</v>
       </c>
       <c r="E23">
-        <v>-33.35283807261284</v>
+        <v>-36.31109541744156</v>
       </c>
       <c r="F23">
-        <v>5.016712957379704</v>
+        <v>2.973210097943992</v>
       </c>
       <c r="G23">
-        <v>-11.61420088156275</v>
+        <v>-11.89964746990509</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.002412483041021</v>
       </c>
       <c r="E24">
-        <v>-32.87644487124292</v>
+        <v>-36.80850979515508</v>
       </c>
       <c r="F24">
-        <v>5.484550015458781</v>
+        <v>2.992984884583622</v>
       </c>
       <c r="G24">
-        <v>-11.81238338253165</v>
+        <v>-14.02034854148682</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.8793613301304</v>
       </c>
       <c r="E25">
-        <v>-33.75516355311331</v>
+        <v>-35.73604488134053</v>
       </c>
       <c r="F25">
-        <v>5.380382814556743</v>
+        <v>2.518128241133223</v>
       </c>
       <c r="G25">
-        <v>-10.70626718873504</v>
+        <v>-12.78654197009364</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.713564628663286</v>
       </c>
       <c r="E26">
-        <v>-34.08729315802087</v>
+        <v>-37.53973381435863</v>
       </c>
       <c r="F26">
-        <v>5.629471235843749</v>
+        <v>3.101751181306003</v>
       </c>
       <c r="G26">
-        <v>-11.15266753823282</v>
+        <v>-12.8677029853665</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.512884675280982</v>
       </c>
       <c r="E27">
-        <v>-33.87234687500979</v>
+        <v>-36.31918553625626</v>
       </c>
       <c r="F27">
-        <v>5.403707983884772</v>
+        <v>3.126509426240875</v>
       </c>
       <c r="G27">
-        <v>-10.61004208528277</v>
+        <v>-12.41592799495436</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.28623362649957</v>
       </c>
       <c r="E28">
-        <v>-34.02073364705613</v>
+        <v>-36.59290009070188</v>
       </c>
       <c r="F28">
-        <v>5.345256723208433</v>
+        <v>2.444186510024533</v>
       </c>
       <c r="G28">
-        <v>-10.68630095554582</v>
+        <v>-13.15292973186435</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.046585781831841</v>
       </c>
       <c r="E29">
-        <v>-33.10248591557279</v>
+        <v>-36.43124715405007</v>
       </c>
       <c r="F29">
-        <v>5.400984311864367</v>
+        <v>2.731689641248963</v>
       </c>
       <c r="G29">
-        <v>-11.29644082330301</v>
+        <v>-12.71500805887618</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.810323340958954</v>
       </c>
       <c r="E30">
-        <v>-32.61540551554477</v>
+        <v>-35.42977286301677</v>
       </c>
       <c r="F30">
-        <v>5.290983747711815</v>
+        <v>2.183752768788785</v>
       </c>
       <c r="G30">
-        <v>-10.00565748014085</v>
+        <v>-12.54704888969133</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.590149908359367</v>
       </c>
       <c r="E31">
-        <v>-33.07327499398632</v>
+        <v>-35.91149154981971</v>
       </c>
       <c r="F31">
-        <v>4.942428282166255</v>
+        <v>2.54764628516458</v>
       </c>
       <c r="G31">
-        <v>-10.21872032088183</v>
+        <v>-11.71973809180073</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.400732506308757</v>
       </c>
       <c r="E32">
-        <v>-31.23282843744796</v>
+        <v>-35.50321112599916</v>
       </c>
       <c r="F32">
-        <v>5.005513430093855</v>
+        <v>2.265858889019467</v>
       </c>
       <c r="G32">
-        <v>-9.94148334888123</v>
+        <v>-11.56858862066491</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.251892504658742</v>
       </c>
       <c r="E33">
-        <v>-32.23776474686012</v>
+        <v>-36.06555702827166</v>
       </c>
       <c r="F33">
-        <v>4.843040761178371</v>
+        <v>1.633701902716663</v>
       </c>
       <c r="G33">
-        <v>-10.17102448429374</v>
+        <v>-11.37513435996317</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.148489239695989</v>
       </c>
       <c r="E34">
-        <v>-31.7767751498273</v>
+        <v>-34.87519102943041</v>
       </c>
       <c r="F34">
-        <v>4.79828904060953</v>
+        <v>2.046797129349137</v>
       </c>
       <c r="G34">
-        <v>-9.848772433719118</v>
+        <v>-11.10310796779897</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.093841345932636</v>
       </c>
       <c r="E35">
-        <v>-31.26135555945928</v>
+        <v>-34.64319504178046</v>
       </c>
       <c r="F35">
-        <v>4.510423084462674</v>
+        <v>1.871763097137602</v>
       </c>
       <c r="G35">
-        <v>-9.800033168675126</v>
+        <v>-11.83940096085212</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.083321086172202</v>
       </c>
       <c r="E36">
-        <v>-30.82303776754585</v>
+        <v>-33.97003738054026</v>
       </c>
       <c r="F36">
-        <v>4.491856057496326</v>
+        <v>2.5405504899922</v>
       </c>
       <c r="G36">
-        <v>-9.235092127899293</v>
+        <v>-11.74315617007049</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.109386047336531</v>
       </c>
       <c r="E37">
-        <v>-30.71178901083642</v>
+        <v>-34.72269693145912</v>
       </c>
       <c r="F37">
-        <v>4.240635418514515</v>
+        <v>2.532911285803582</v>
       </c>
       <c r="G37">
-        <v>-9.613748377080771</v>
+        <v>-11.96632845443612</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.160428518043628</v>
       </c>
       <c r="E38">
-        <v>-29.78449791675976</v>
+        <v>-32.94049560760742</v>
       </c>
       <c r="F38">
-        <v>4.324842278478696</v>
+        <v>1.626292984666024</v>
       </c>
       <c r="G38">
-        <v>-10.02205046305184</v>
+        <v>-11.32036092847136</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.218998525784143</v>
       </c>
       <c r="E39">
-        <v>-29.51031013678034</v>
+        <v>-32.93488482831191</v>
       </c>
       <c r="F39">
-        <v>4.463277382099744</v>
+        <v>1.435589554663133</v>
       </c>
       <c r="G39">
-        <v>-9.564149431988206</v>
+        <v>-11.38903361448898</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.270011067589055</v>
       </c>
       <c r="E40">
-        <v>-29.20980060163134</v>
+        <v>-31.99249806613069</v>
       </c>
       <c r="F40">
-        <v>4.308286527566344</v>
+        <v>2.24166724738811</v>
       </c>
       <c r="G40">
-        <v>-9.699549039638692</v>
+        <v>-11.34035669265462</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.29650885810719</v>
       </c>
       <c r="E41">
-        <v>-29.40825644654349</v>
+        <v>-29.57964333807478</v>
       </c>
       <c r="F41">
-        <v>3.988869713781661</v>
+        <v>2.351752305015748</v>
       </c>
       <c r="G41">
-        <v>-9.40842265677696</v>
+        <v>-12.78881913785589</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.286272147741984</v>
       </c>
       <c r="E42">
-        <v>-27.96505442266898</v>
+        <v>-30.10024576694458</v>
       </c>
       <c r="F42">
-        <v>3.942732962915339</v>
+        <v>1.781152957149781</v>
       </c>
       <c r="G42">
-        <v>-9.621275499338138</v>
+        <v>-12.19071807200031</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.231805275000435</v>
       </c>
       <c r="E43">
-        <v>-26.87004223677024</v>
+        <v>-30.82174715245366</v>
       </c>
       <c r="F43">
-        <v>4.306460805810574</v>
+        <v>1.777821263455721</v>
       </c>
       <c r="G43">
-        <v>-9.61252120021754</v>
+        <v>-11.87884124399665</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.129033536821157</v>
       </c>
       <c r="E44">
-        <v>-26.62806775664438</v>
+        <v>-30.07301378849946</v>
       </c>
       <c r="F44">
-        <v>4.026741014702848</v>
+        <v>2.035531332671064</v>
       </c>
       <c r="G44">
-        <v>-9.775860409446697</v>
+        <v>-11.89726530305293</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.981964151352204</v>
       </c>
       <c r="E45">
-        <v>-26.61865305918244</v>
+        <v>-30.67952136929476</v>
       </c>
       <c r="F45">
-        <v>4.167613175222932</v>
+        <v>2.122246489130922</v>
       </c>
       <c r="G45">
-        <v>-9.301553270585845</v>
+        <v>-12.11991259196905</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.797944582455656</v>
       </c>
       <c r="E46">
-        <v>-25.99851930009805</v>
+        <v>-28.65453723270683</v>
       </c>
       <c r="F46">
-        <v>4.326399609195959</v>
+        <v>2.420745369260113</v>
       </c>
       <c r="G46">
-        <v>-9.443200324085513</v>
+        <v>-12.14805891050597</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.588730076153846</v>
       </c>
       <c r="E47">
-        <v>-25.76176615050304</v>
+        <v>-28.94293309988532</v>
       </c>
       <c r="F47">
-        <v>3.852724217661951</v>
+        <v>2.318758431362243</v>
       </c>
       <c r="G47">
-        <v>-9.490814130134616</v>
+        <v>-13.12952477848083</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.370340966861434</v>
       </c>
       <c r="E48">
-        <v>-24.72241343863258</v>
+        <v>-29.42848966840976</v>
       </c>
       <c r="F48">
-        <v>3.800402875766328</v>
+        <v>2.200883406678679</v>
       </c>
       <c r="G48">
-        <v>-9.546017401650714</v>
+        <v>-12.96883351505015</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.15826408470151</v>
       </c>
       <c r="E49">
-        <v>-24.12959090628845</v>
+        <v>-28.43444433898604</v>
       </c>
       <c r="F49">
-        <v>3.689948366277042</v>
+        <v>1.945688260898235</v>
       </c>
       <c r="G49">
-        <v>-9.796427106181296</v>
+        <v>-12.28965346446069</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.9682752623204982</v>
       </c>
       <c r="E50">
-        <v>-24.38168199734744</v>
+        <v>-26.30658232989185</v>
       </c>
       <c r="F50">
-        <v>4.173655287058952</v>
+        <v>1.994137813553173</v>
       </c>
       <c r="G50">
-        <v>-9.417551015155334</v>
+        <v>-12.57384990738887</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.8144133687135444</v>
       </c>
       <c r="E51">
-        <v>-23.33103074282784</v>
+        <v>-25.3135785494899</v>
       </c>
       <c r="F51">
-        <v>3.978264954291022</v>
+        <v>1.654787166587522</v>
       </c>
       <c r="G51">
-        <v>-9.07243213153294</v>
+        <v>-11.58226147090312</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.7058432626636475</v>
       </c>
       <c r="E52">
-        <v>-22.24016663912013</v>
+        <v>-25.23731904720073</v>
       </c>
       <c r="F52">
-        <v>3.72530143029372</v>
+        <v>2.228317278324593</v>
       </c>
       <c r="G52">
-        <v>-9.889292238756701</v>
+        <v>-12.75291273033089</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.6496168363006163</v>
       </c>
       <c r="E53">
-        <v>-22.10695251923649</v>
+        <v>-27.08135441939017</v>
       </c>
       <c r="F53">
-        <v>4.191620919290868</v>
+        <v>1.896657194326533</v>
       </c>
       <c r="G53">
-        <v>-10.03366270615071</v>
+        <v>-13.41066312291562</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.6480899422197087</v>
       </c>
       <c r="E54">
-        <v>-22.28843111509388</v>
+        <v>-26.41714049431512</v>
       </c>
       <c r="F54">
-        <v>3.988019808826389</v>
+        <v>2.055060922559465</v>
       </c>
       <c r="G54">
-        <v>-10.1528563605191</v>
+        <v>-12.7679932246181</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.6993041275372693</v>
       </c>
       <c r="E55">
-        <v>-21.10852362697335</v>
+        <v>-24.99875450800264</v>
       </c>
       <c r="F55">
-        <v>3.94802954408884</v>
+        <v>2.18978162674636</v>
       </c>
       <c r="G55">
-        <v>-9.811199165641916</v>
+        <v>-13.29410428945946</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.8006877938882129</v>
       </c>
       <c r="E56">
-        <v>-21.4738854383862</v>
+        <v>-24.25272464303102</v>
       </c>
       <c r="F56">
-        <v>3.762457021778889</v>
+        <v>2.080867880626281</v>
       </c>
       <c r="G56">
-        <v>-9.768405474063639</v>
+        <v>-12.7751692561686</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-0.9457365941747691</v>
       </c>
       <c r="E57">
-        <v>-20.59590489777907</v>
+        <v>-23.44000394134842</v>
       </c>
       <c r="F57">
-        <v>4.061381682753118</v>
+        <v>2.339151180084361</v>
       </c>
       <c r="G57">
-        <v>-10.03600549834415</v>
+        <v>-12.27919621135073</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-1.127090714870266</v>
       </c>
       <c r="E58">
-        <v>-20.13644592496084</v>
+        <v>-24.4318393754564</v>
       </c>
       <c r="F58">
-        <v>4.02038246651896</v>
+        <v>2.290275846584385</v>
       </c>
       <c r="G58">
-        <v>-10.11529621732813</v>
+        <v>-12.25838342299918</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-1.338095134724402</v>
       </c>
       <c r="E59">
-        <v>-20.94320262637532</v>
+        <v>-23.13843927175563</v>
       </c>
       <c r="F59">
-        <v>3.943538136030861</v>
+        <v>1.748995734573104</v>
       </c>
       <c r="G59">
-        <v>-10.82934580942982</v>
+        <v>-13.39047048543879</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-1.569166838745946</v>
       </c>
       <c r="E60">
-        <v>-19.58049875646117</v>
+        <v>-22.73464430143968</v>
       </c>
       <c r="F60">
-        <v>3.835727775291311</v>
+        <v>2.361631414661534</v>
       </c>
       <c r="G60">
-        <v>-10.65001392631992</v>
+        <v>-13.52863944408545</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-1.811972455713114</v>
       </c>
       <c r="E61">
-        <v>-19.58211542168191</v>
+        <v>-22.13943979176752</v>
       </c>
       <c r="F61">
-        <v>3.80586844389</v>
+        <v>1.767027636197244</v>
       </c>
       <c r="G61">
-        <v>-10.82069322817756</v>
+        <v>-13.63641116620541</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.058636229813706</v>
       </c>
       <c r="E62">
-        <v>-19.13958841317835</v>
+        <v>-19.96239855495003</v>
       </c>
       <c r="F62">
-        <v>3.639739361258559</v>
+        <v>1.608211380997717</v>
       </c>
       <c r="G62">
-        <v>-10.75091477049441</v>
+        <v>-14.12391209695679</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.298511350945899</v>
       </c>
       <c r="E63">
-        <v>-18.31698658121103</v>
+        <v>-20.97002930639676</v>
       </c>
       <c r="F63">
-        <v>3.596715615091958</v>
+        <v>1.785505199484089</v>
       </c>
       <c r="G63">
-        <v>-10.81589936347921</v>
+        <v>-14.46396477449141</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.525301680945593</v>
       </c>
       <c r="E64">
-        <v>-18.40171432989453</v>
+        <v>-20.7882110749888</v>
       </c>
       <c r="F64">
-        <v>3.641364618102851</v>
+        <v>1.92502712113761</v>
       </c>
       <c r="G64">
-        <v>-10.67571901601661</v>
+        <v>-14.32742986418135</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.730390490258675</v>
       </c>
       <c r="E65">
-        <v>-18.06969114412615</v>
+        <v>-21.37890975302333</v>
       </c>
       <c r="F65">
-        <v>3.85002539666363</v>
+        <v>1.429158110147798</v>
       </c>
       <c r="G65">
-        <v>-11.33108067930607</v>
+        <v>-14.73126948883157</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.906155834974586</v>
       </c>
       <c r="E66">
-        <v>-18.09421283087769</v>
+        <v>-20.02682968313117</v>
       </c>
       <c r="F66">
-        <v>3.55329922277643</v>
+        <v>1.634826825649665</v>
       </c>
       <c r="G66">
-        <v>-11.32451823618718</v>
+        <v>-14.34552251986013</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.04637111176031</v>
       </c>
       <c r="E67">
-        <v>-18.31104069483895</v>
+        <v>-20.6240855915288</v>
       </c>
       <c r="F67">
-        <v>3.49068127406401</v>
+        <v>1.493833723488772</v>
       </c>
       <c r="G67">
-        <v>-11.47227492423053</v>
+        <v>-13.64381688326508</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.143944529867329</v>
       </c>
       <c r="E68">
-        <v>-18.06484114846394</v>
+        <v>-21.06245546089332</v>
       </c>
       <c r="F68">
-        <v>3.184241664011584</v>
+        <v>2.08677082673863</v>
       </c>
       <c r="G68">
-        <v>-11.03090468738339</v>
+        <v>-13.5843808359373</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.193979037494669</v>
       </c>
       <c r="E69">
-        <v>-19.01959743739711</v>
+        <v>-22.13091267521107</v>
       </c>
       <c r="F69">
-        <v>3.36359314712651</v>
+        <v>1.830674417223941</v>
       </c>
       <c r="G69">
-        <v>-11.54398930263376</v>
+        <v>-13.0570425942327</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.190910440407461</v>
       </c>
       <c r="E70">
-        <v>-18.5459824548309</v>
+        <v>-22.28536986666469</v>
       </c>
       <c r="F70">
-        <v>3.509428885124168</v>
+        <v>1.510096232340532</v>
       </c>
       <c r="G70">
-        <v>-11.0640187753613</v>
+        <v>-14.58004783082144</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.131909714974332</v>
       </c>
       <c r="E71">
-        <v>-17.98158062535891</v>
+        <v>-20.40661015578444</v>
       </c>
       <c r="F71">
-        <v>2.960191475841595</v>
+        <v>1.527725547406911</v>
       </c>
       <c r="G71">
-        <v>-10.49359809458119</v>
+        <v>-14.15077545786397</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.013370330884769</v>
       </c>
       <c r="E72">
-        <v>-17.64797700216185</v>
+        <v>-20.35105030818433</v>
       </c>
       <c r="F72">
-        <v>3.184475263619173</v>
+        <v>1.939172322907815</v>
       </c>
       <c r="G72">
-        <v>-11.41931928948265</v>
+        <v>-12.81632561818872</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.834486305890499</v>
       </c>
       <c r="E73">
-        <v>-18.36524652871077</v>
+        <v>-21.65164615708329</v>
       </c>
       <c r="F73">
-        <v>2.816063831428509</v>
+        <v>1.437741653175607</v>
       </c>
       <c r="G73">
-        <v>-11.25447071833615</v>
+        <v>-13.467979501116</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.596661633727071</v>
       </c>
       <c r="E74">
-        <v>-18.20965269028122</v>
+        <v>-22.13968885783794</v>
       </c>
       <c r="F74">
-        <v>3.128835481907936</v>
+        <v>0.999407728514637</v>
       </c>
       <c r="G74">
-        <v>-11.35932215326821</v>
+        <v>-12.93842643485877</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.300383174223771</v>
       </c>
       <c r="E75">
-        <v>-17.74472332086172</v>
+        <v>-20.19855394597603</v>
       </c>
       <c r="F75">
-        <v>2.901226627375521</v>
+        <v>1.296574593860126</v>
       </c>
       <c r="G75">
-        <v>-10.3343800996307</v>
+        <v>-13.14632135164363</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.95383677492465</v>
       </c>
       <c r="E76">
-        <v>-18.27923722188308</v>
+        <v>-22.61114375830249</v>
       </c>
       <c r="F76">
-        <v>2.967166329373168</v>
+        <v>1.441596875068236</v>
       </c>
       <c r="G76">
-        <v>-10.44487851686656</v>
+        <v>-12.75782800022694</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.560858089197731</v>
       </c>
       <c r="E77">
-        <v>-19.18178926245583</v>
+        <v>-22.3824331785451</v>
       </c>
       <c r="F77">
-        <v>2.589909590055411</v>
+        <v>1.24648321701284</v>
       </c>
       <c r="G77">
-        <v>-10.56073516890899</v>
+        <v>-12.19784488522742</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.129198811263592</v>
       </c>
       <c r="E78">
-        <v>-19.03789700086211</v>
+        <v>-23.22870534415052</v>
       </c>
       <c r="F78">
-        <v>2.989474263530558</v>
+        <v>1.40870903244229</v>
       </c>
       <c r="G78">
-        <v>-10.43818810610685</v>
+        <v>-11.81486070480904</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.6691291322307235</v>
       </c>
       <c r="E79">
-        <v>-18.79239483948427</v>
+        <v>-20.98796206346714</v>
       </c>
       <c r="F79">
-        <v>2.345064066605544</v>
+        <v>0.5413487192582056</v>
       </c>
       <c r="G79">
-        <v>-9.537243415200759</v>
+        <v>-11.83319617088321</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.1846973159571805</v>
       </c>
       <c r="E80">
-        <v>-20.10233745873506</v>
+        <v>-21.85876950124612</v>
       </c>
       <c r="F80">
-        <v>2.201179962208881</v>
+        <v>1.483132873379408</v>
       </c>
       <c r="G80">
-        <v>-9.530763002620855</v>
+        <v>-11.87302035695019</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.3111659475540834</v>
       </c>
       <c r="E81">
-        <v>-19.55689182145918</v>
+        <v>-23.97466275353803</v>
       </c>
       <c r="F81">
-        <v>2.567222263627538</v>
+        <v>0.5886186767315565</v>
       </c>
       <c r="G81">
-        <v>-8.77555704849906</v>
+        <v>-11.58550003658229</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.8130602813111052</v>
       </c>
       <c r="E82">
-        <v>-20.24766524658922</v>
+        <v>-22.28567327442321</v>
       </c>
       <c r="F82">
-        <v>2.420339469232741</v>
+        <v>1.334391222532729</v>
       </c>
       <c r="G82">
-        <v>-8.676060567152017</v>
+        <v>-11.30271451892467</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.314975315406335</v>
       </c>
       <c r="E83">
-        <v>-21.15541597532278</v>
+        <v>-25.66213066538628</v>
       </c>
       <c r="F83">
-        <v>2.535628330884765</v>
+        <v>0.6028773648359445</v>
       </c>
       <c r="G83">
-        <v>-8.802315410316332</v>
+        <v>-10.3044848900026</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.805027625774732</v>
       </c>
       <c r="E84">
-        <v>-22.12236291628459</v>
+        <v>-24.75077979981662</v>
       </c>
       <c r="F84">
-        <v>2.203968246886705</v>
+        <v>0.07551713866130638</v>
       </c>
       <c r="G84">
-        <v>-8.776013138295824</v>
+        <v>-10.76483699357113</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.280080417834599</v>
       </c>
       <c r="E85">
-        <v>-23.08131710062288</v>
+        <v>-27.29091861104312</v>
       </c>
       <c r="F85">
-        <v>2.051909812959216</v>
+        <v>0.358696192043123</v>
       </c>
       <c r="G85">
-        <v>-7.81072041138746</v>
+        <v>-10.3241131573712</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.728664857378931</v>
       </c>
       <c r="E86">
-        <v>-23.79728242665758</v>
+        <v>-26.44856810392835</v>
       </c>
       <c r="F86">
-        <v>1.943219726037893</v>
+        <v>-0.4495393977661463</v>
       </c>
       <c r="G86">
-        <v>-8.94455636491826</v>
+        <v>-9.782353946912838</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.142560669356529</v>
       </c>
       <c r="E87">
-        <v>-24.94338938478487</v>
+        <v>-28.19169548980487</v>
       </c>
       <c r="F87">
-        <v>1.715746723759537</v>
+        <v>0.2881921856560514</v>
       </c>
       <c r="G87">
-        <v>-8.333635566429926</v>
+        <v>-10.54018815950375</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>3.51543241296078</v>
       </c>
       <c r="E88">
-        <v>-25.80472778341381</v>
+        <v>-29.02583134506973</v>
       </c>
       <c r="F88">
-        <v>1.654319967372343</v>
+        <v>0.5072083851192267</v>
       </c>
       <c r="G88">
-        <v>-7.534956707867048</v>
+        <v>-9.87399846506813</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>3.835395790788426</v>
       </c>
       <c r="E89">
-        <v>-27.38879704824491</v>
+        <v>-29.75861089509492</v>
       </c>
       <c r="F89">
-        <v>1.452851074602669</v>
+        <v>-0.06902468945317936</v>
       </c>
       <c r="G89">
-        <v>-7.1427621385313</v>
+        <v>-9.248778103023737</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>4.098069584560332</v>
       </c>
       <c r="E90">
-        <v>-28.321658165351</v>
+        <v>-30.82234717525968</v>
       </c>
       <c r="F90">
-        <v>0.8528479974069316</v>
+        <v>-0.3629385560078747</v>
       </c>
       <c r="G90">
-        <v>-7.65891797716131</v>
+        <v>-10.27230595016912</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>4.296227010602268</v>
       </c>
       <c r="E91">
-        <v>-29.76172195673819</v>
+        <v>-29.92665577280856</v>
       </c>
       <c r="F91">
-        <v>0.6323134004944249</v>
+        <v>-0.6971848030374752</v>
       </c>
       <c r="G91">
-        <v>-7.696947335035274</v>
+        <v>-9.432624946999423</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>4.423918193870221</v>
       </c>
       <c r="E92">
-        <v>-31.68868727343009</v>
+        <v>-34.18869701223763</v>
       </c>
       <c r="F92">
-        <v>0.42335192456643</v>
+        <v>-1.281617886530194</v>
       </c>
       <c r="G92">
-        <v>-7.66518182911829</v>
+        <v>-10.63718763124406</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.475703293136769</v>
       </c>
       <c r="E93">
-        <v>-32.59029059869824</v>
+        <v>-35.82825366908472</v>
       </c>
       <c r="F93">
-        <v>-0.07282275399501509</v>
+        <v>-1.375370024076833</v>
       </c>
       <c r="G93">
-        <v>-7.394999483470493</v>
+        <v>-10.30958390830597</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.4449529796213</v>
       </c>
       <c r="E94">
-        <v>-35.39659046972557</v>
+        <v>-36.64708328220365</v>
       </c>
       <c r="F94">
-        <v>-0.1208051074347737</v>
+        <v>-1.508019809756729</v>
       </c>
       <c r="G94">
-        <v>-7.613860242707015</v>
+        <v>-10.4526911053996</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.330268608714993</v>
       </c>
       <c r="E95">
-        <v>-37.20110132077605</v>
+        <v>-39.08439629837499</v>
       </c>
       <c r="F95">
-        <v>-0.4982051543132144</v>
+        <v>-2.349983206738383</v>
       </c>
       <c r="G95">
-        <v>-7.494177686326269</v>
+        <v>-10.38507169150256</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.124449944841118</v>
       </c>
       <c r="E96">
-        <v>-37.80313250501478</v>
+        <v>-41.22251530109655</v>
       </c>
       <c r="F96">
-        <v>-0.7792710424504895</v>
+        <v>-2.777977449477609</v>
       </c>
       <c r="G96">
-        <v>-7.322284332491638</v>
+        <v>-10.51182528034391</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.837812751456035</v>
       </c>
       <c r="E97">
-        <v>-40.86953433762067</v>
+        <v>-42.30470511284257</v>
       </c>
       <c r="F97">
-        <v>-1.313701384408021</v>
+        <v>-2.947811819501772</v>
       </c>
       <c r="G97">
-        <v>-7.463498264745461</v>
+        <v>-9.741702893012878</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.46291390337384</v>
       </c>
       <c r="E98">
-        <v>-42.18048001386416</v>
+        <v>-45.30586522041995</v>
       </c>
       <c r="F98">
-        <v>-2.039302355583623</v>
+        <v>-2.859164081891183</v>
       </c>
       <c r="G98">
-        <v>-8.089555338287512</v>
+        <v>-11.009301124636</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.032189712803306</v>
       </c>
       <c r="E99">
-        <v>-44.36692009848456</v>
+        <v>-45.33955027432601</v>
       </c>
       <c r="F99">
-        <v>-2.284871872143536</v>
+        <v>-3.659249364824308</v>
       </c>
       <c r="G99">
-        <v>-8.014920672696384</v>
+        <v>-11.46234594779165</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>2.531107392131358</v>
       </c>
       <c r="E100">
-        <v>-47.60235854461177</v>
+        <v>-48.15170546224525</v>
       </c>
       <c r="F100">
-        <v>-2.713908201075484</v>
+        <v>-3.587037264852664</v>
       </c>
       <c r="G100">
-        <v>-8.836528707516662</v>
+        <v>-11.94223444452512</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>2.029842140582093</v>
       </c>
       <c r="E101">
-        <v>-48.86848025300883</v>
+        <v>-50.71062611941857</v>
       </c>
       <c r="F101">
-        <v>-2.981101420318076</v>
+        <v>-4.31284367114416</v>
       </c>
       <c r="G101">
-        <v>-8.561463904188411</v>
+        <v>-11.63202447707366</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.464185644177064</v>
       </c>
       <c r="E102">
-        <v>-50.80721507364667</v>
+        <v>-52.92565672468641</v>
       </c>
       <c r="F102">
-        <v>-3.39795743495926</v>
+        <v>-4.341724700642765</v>
       </c>
       <c r="G102">
-        <v>-9.589404994331252</v>
+        <v>-12.93682519873776</v>
       </c>
     </row>
   </sheetData>
